--- a/KatalonData/IWPBootstrapData/vRelayPaymentsACH.xlsx
+++ b/KatalonData/IWPBootstrapData/vRelayPaymentsACH.xlsx
@@ -72,7 +72,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2201" uniqueCount="299">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2439" uniqueCount="418">
   <si>
     <t>Result</t>
   </si>
@@ -969,6 +969,363 @@
   </si>
   <si>
     <t>Wed Jun 24 15:25:41 EDT 2026</t>
+  </si>
+  <si>
+    <t>Tue Aug 18 19:58:16 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Aug 18 20:00:45 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Aug 18 20:03:33 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Aug 18 20:07:23 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Aug 18 20:08:50 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Aug 18 20:10:32 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Aug 18 20:15:19 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Aug 18 20:16:41 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Aug 18 20:18:19 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Aug 18 20:20:35 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Aug 18 20:21:56 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Aug 18 20:25:55 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Aug 18 20:27:14 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Aug 18 20:28:32 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Aug 18 20:37:11 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Aug 18 20:38:25 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Aug 18 20:39:40 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Aug 18 20:42:15 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Aug 18 20:43:51 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Aug 18 20:45:26 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Aug 18 20:50:14 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Aug 18 20:52:21 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Aug 18 20:56:35 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Aug 18 21:00:59 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Aug 18 21:03:12 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Aug 18 21:09:30 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Aug 18 21:12:38 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Aug 18 21:13:43 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Aug 18 21:14:17 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Aug 18 21:17:54 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Aug 18 21:18:58 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Aug 18 21:20:02 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Aug 18 21:28:24 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Aug 18 21:30:54 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Aug 18 21:35:05 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Aug 18 21:39:31 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Aug 18 21:43:27 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Aug 18 21:45:08 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Aug 18 21:47:40 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Aug 18 21:49:06 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Aug 18 21:54:07 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Aug 18 21:55:41 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Aug 18 21:59:24 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Aug 18 22:01:01 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Aug 18 22:02:39 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Aug 18 22:05:30 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Aug 18 22:08:01 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Aug 18 22:11:33 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Aug 18 22:12:52 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Aug 18 22:15:47 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Aug 18 22:17:09 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Aug 18 23:34:09 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Aug 19 00:07:48 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Aug 19 00:12:04 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Aug 19 00:16:38 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Aug 19 00:19:32 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Aug 19 00:21:06 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Aug 19 00:25:37 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Aug 19 17:36:57 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Aug 19 22:35:33 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Aug 19 22:38:00 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Aug 19 22:40:19 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Aug 19 22:44:05 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Aug 19 22:45:30 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Aug 19 22:47:16 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Aug 19 22:51:41 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Aug 19 22:52:52 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Aug 19 22:54:08 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Aug 19 22:57:03 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Aug 19 22:58:18 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Aug 19 23:02:15 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Aug 19 23:03:28 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Aug 19 23:04:51 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Aug 19 23:14:00 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Aug 19 23:15:18 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Aug 19 23:16:30 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Aug 19 23:18:53 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Aug 19 23:20:11 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Aug 19 23:21:28 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Aug 19 23:25:58 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Aug 19 23:28:19 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Aug 19 23:30:26 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Aug 19 23:35:15 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Aug 19 23:37:35 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Aug 19 23:43:45 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Aug 19 23:48:14 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Aug 19 23:49:16 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Aug 19 23:49:46 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Aug 19 23:50:14 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Aug 19 23:50:44 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Aug 19 23:56:50 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Aug 19 23:57:44 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Aug 19 23:58:44 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Aug 19 23:59:36 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Aug 20 00:07:22 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Aug 20 00:09:31 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Aug 20 00:20:54 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Aug 20 00:26:54 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Aug 20 00:30:15 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Aug 20 00:31:41 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Aug 20 00:34:42 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Aug 20 00:36:02 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Aug 20 00:38:46 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Aug 20 00:40:15 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Aug 20 00:43:14 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Aug 20 00:44:48 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Aug 20 00:46:18 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Aug 20 00:50:41 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Aug 20 00:54:12 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Aug 20 00:55:55 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Aug 20 00:59:23 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Aug 20 01:01:05 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Aug 20 02:28:43 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Aug 20 03:02:22 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Aug 20 03:07:44 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Aug 20 03:13:06 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Aug 20 03:16:08 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Aug 20 03:17:50 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Aug 20 03:22:37 IST 2026</t>
   </si>
 </sst>
 </file>
@@ -1362,7 +1719,7 @@
         <v>21</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>298</v>
+        <v>373</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -1459,7 +1816,7 @@
         <v>21</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>238</v>
+        <v>377</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -1553,7 +1910,7 @@
         <v>21</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>236</v>
+        <v>375</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -1647,7 +2004,7 @@
         <v>21</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>231</v>
+        <v>370</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -1741,7 +2098,7 @@
         <v>21</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>232</v>
+        <v>371</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -1835,7 +2192,7 @@
         <v>21</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>230</v>
+        <v>369</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -1929,7 +2286,7 @@
         <v>21</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>291</v>
+        <v>392</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -2023,7 +2380,7 @@
         <v>21</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>250</v>
+        <v>391</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -2117,7 +2474,7 @@
         <v>21</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>249</v>
+        <v>389</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -2211,7 +2568,7 @@
         <v>21</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>248</v>
+        <v>388</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -2305,7 +2662,7 @@
         <v>21</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>247</v>
+        <v>387</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -2399,7 +2756,7 @@
         <v>21</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>235</v>
+        <v>374</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -2529,7 +2886,7 @@
         <v>21</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>246</v>
+        <v>384</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -2666,7 +3023,7 @@
         <v>21</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>212</v>
+        <v>360</v>
       </c>
       <c r="D3" t="s" s="0">
         <v>14</v>
@@ -2762,7 +3119,7 @@
         <v>21</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>284</v>
+        <v>406</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -2856,7 +3213,7 @@
         <v>21</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>240</v>
+        <v>380</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -2950,7 +3307,7 @@
         <v>21</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>257</v>
+        <v>394</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -3044,7 +3401,7 @@
         <v>21</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>245</v>
+        <v>383</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -3138,7 +3495,7 @@
         <v>21</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>259</v>
+        <v>396</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -3232,7 +3589,7 @@
         <v>21</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>280</v>
+        <v>405</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -3326,7 +3683,7 @@
         <v>21</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>239</v>
+        <v>379</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -3420,7 +3777,7 @@
         <v>21</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>253</v>
+        <v>393</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -3514,7 +3871,7 @@
         <v>21</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>233</v>
+        <v>372</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -3641,10 +3998,10 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" t="s" s="0">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>242</v>
+        <v>381</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -3735,10 +4092,10 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" t="s" s="0">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>258</v>
+        <v>395</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -3832,7 +4189,7 @@
         <v>21</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>224</v>
+        <v>363</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -3931,7 +4288,7 @@
         <v>21</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>220</v>
+        <v>362</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -4030,7 +4387,7 @@
         <v>21</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>261</v>
+        <v>412</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -4129,7 +4486,7 @@
         <v>21</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>263</v>
+        <v>413</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -4228,7 +4585,7 @@
         <v>21</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>271</v>
+        <v>414</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -4327,7 +4684,7 @@
         <v>21</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>279</v>
+        <v>416</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -4423,7 +4780,7 @@
         <v>21</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>297</v>
+        <v>361</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -4519,7 +4876,7 @@
         <v>21</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>260</v>
+        <v>397</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -4615,7 +4972,7 @@
         <v>21</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>286</v>
+        <v>407</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -4709,7 +5066,7 @@
         <v>21</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>290</v>
+        <v>399</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -4805,7 +5162,7 @@
         <v>21</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>267</v>
+        <v>401</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -4901,7 +5258,7 @@
         <v>21</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>275</v>
+        <v>415</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -5000,7 +5357,7 @@
         <v>21</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>226</v>
+        <v>365</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -5092,7 +5449,7 @@
         <v>21</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>227</v>
+        <v>366</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -5184,7 +5541,7 @@
         <v>21</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>225</v>
+        <v>364</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -5276,7 +5633,7 @@
         <v>21</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>229</v>
+        <v>368</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -5368,7 +5725,7 @@
         <v>21</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>201</v>
+        <v>411</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -5460,7 +5817,7 @@
         <v>21</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>228</v>
+        <v>367</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -5555,7 +5912,7 @@
         <v>21</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>289</v>
+        <v>410</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -5652,7 +6009,7 @@
         <v>21</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>287</v>
+        <v>417</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -5840,7 +6197,7 @@
         <v>21</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>288</v>
+        <v>409</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -5934,7 +6291,7 @@
         <v>21</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>237</v>
+        <v>376</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">

--- a/KatalonData/IWPBootstrapData/vRelayPaymentsACH.xlsx
+++ b/KatalonData/IWPBootstrapData/vRelayPaymentsACH.xlsx
@@ -72,7 +72,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2439" uniqueCount="418">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2831" uniqueCount="614">
   <si>
     <t>Result</t>
   </si>
@@ -1326,6 +1326,594 @@
   </si>
   <si>
     <t>Thu Aug 20 03:22:37 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 01 22:57:27 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 01 23:00:59 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 01 23:04:17 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 01 23:14:15 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 01 23:15:43 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 01 23:17:05 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 01 23:18:48 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 01 23:26:34 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 01 23:27:54 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 01 23:29:11 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 01 23:34:49 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 01 23:36:17 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 01 23:43:36 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 01 23:44:52 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 01 23:46:08 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 01 23:51:49 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 01 23:53:13 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 01 23:54:46 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 02 00:00:46 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 02 00:02:04 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 02 00:03:21 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 02 00:10:21 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 02 00:12:24 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 02 00:14:22 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 02 00:16:28 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 02 00:26:49 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 02 00:32:57 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 02 00:35:02 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 02 00:41:04 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 02 00:42:15 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 02 00:42:44 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 02 00:43:17 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 02 00:53:03 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 02 00:54:13 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 02 00:55:33 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 02 00:56:28 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 02 01:03:47 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 02 01:06:03 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 02 01:14:55 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 02 01:17:12 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 02 01:24:50 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 02 01:33:22 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 02 01:35:08 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 02 01:41:36 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 02 01:45:19 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 02 01:54:39 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 02 01:56:39 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 02 02:03:48 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 02 02:05:17 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 02 02:06:48 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 02 02:09:27 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 02 02:16:19 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 02 02:17:39 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 02 02:23:45 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 02 02:25:32 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Oct 05 01:53:17 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Oct 05 01:55:33 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Oct 05 01:58:02 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Oct 05 02:01:26 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Oct 05 02:02:45 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Oct 05 02:04:01 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Oct 05 02:07:37 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Oct 05 02:08:48 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Oct 05 02:09:53 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Oct 05 02:11:57 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Oct 05 02:13:08 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Oct 05 02:16:31 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Oct 05 02:17:43 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Oct 05 02:18:51 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Oct 05 02:27:08 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Oct 05 02:28:21 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Oct 05 02:29:26 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Oct 05 02:31:37 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Oct 05 02:32:50 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Oct 05 02:34:01 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Oct 05 02:37:56 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Oct 05 02:39:47 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Oct 05 02:47:16 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Oct 05 02:49:16 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Oct 05 02:51:36 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Oct 05 02:54:34 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Oct 05 02:55:28 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Oct 05 02:56:19 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Oct 05 02:57:24 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Oct 05 02:57:55 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Oct 05 03:04:51 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Oct 05 03:05:50 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Oct 05 03:06:45 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Oct 05 03:13:38 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Oct 05 03:15:49 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Oct 05 03:17:46 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Oct 05 03:19:54 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Oct 05 03:22:06 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Oct 05 03:29:14 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Oct 05 03:36:46 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Oct 05 03:40:03 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Oct 05 03:41:22 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Oct 05 03:43:49 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Oct 05 03:45:08 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Oct 05 03:49:28 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Oct 05 03:51:09 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Oct 05 03:53:44 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Oct 05 03:55:08 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Oct 05 03:56:32 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Oct 05 03:58:55 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Oct 05 04:01:21 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Oct 05 04:04:43 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Oct 05 04:06:03 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Oct 05 04:08:22 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Oct 05 04:09:38 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Oct 05 08:05:12 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Oct 05 08:34:24 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Oct 05 08:38:16 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Oct 05 08:42:31 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Oct 05 08:45:36 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Oct 05 08:47:06 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Oct 05 08:51:23 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Oct 05 19:26:58 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Oct 05 19:31:33 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 06 20:24:00 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 06 21:15:25 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 21 07:45:50 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 21 07:48:12 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 21 07:50:27 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 21 07:54:33 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 21 07:56:01 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 21 07:57:50 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 21 08:02:09 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 21 08:03:24 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 21 08:04:50 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 21 08:07:54 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 21 08:09:12 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 21 08:13:12 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 21 08:14:32 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 21 08:16:09 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 21 08:25:38 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 21 08:27:01 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 21 08:28:17 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 21 08:30:59 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 21 08:32:23 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 21 08:33:40 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 21 08:36:42 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 21 08:39:09 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 21 08:41:16 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 21 08:49:26 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 21 08:51:31 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 21 08:54:30 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 21 08:55:27 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 21 08:56:23 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 21 08:57:23 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 21 08:57:54 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 21 08:58:26 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 21 09:05:41 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 21 09:06:46 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 21 09:08:18 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 21 09:09:13 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 21 09:16:39 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 21 09:19:00 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 21 09:27:42 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 21 09:34:24 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 21 09:38:19 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 21 09:39:42 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 21 09:42:31 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 21 09:43:58 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 21 09:48:20 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 21 09:50:00 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 21 09:52:54 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 21 09:54:35 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 21 09:56:13 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 21 09:58:29 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 21 10:00:37 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 21 10:04:16 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 21 10:05:41 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 21 10:09:00 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 21 10:10:36 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 21 16:53:07 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 21 18:28:00 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 21 18:33:46 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 21 18:38:58 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 21 18:42:05 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 21 18:43:47 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 21 18:49:15 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 21 20:09:04 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 21 20:17:47 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 21 20:22:35 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 22 03:33:06 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 22 03:36:03 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 22 04:10:12 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 22 04:11:25 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 23 01:43:01 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 23 02:32:29 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 23 02:37:35 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 23 02:42:07 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 23 02:44:55 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 23 02:46:37 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 23 02:52:20 IST 2026</t>
   </si>
 </sst>
 </file>
@@ -1719,7 +2307,7 @@
         <v>21</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>373</v>
+        <v>554</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -1816,7 +2404,7 @@
         <v>21</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>377</v>
+        <v>558</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -1910,7 +2498,7 @@
         <v>21</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>375</v>
+        <v>556</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -2004,7 +2592,7 @@
         <v>21</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>370</v>
+        <v>551</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -2098,7 +2686,7 @@
         <v>21</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>371</v>
+        <v>552</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -2192,7 +2780,7 @@
         <v>21</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>369</v>
+        <v>550</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -2286,7 +2874,7 @@
         <v>21</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>392</v>
+        <v>605</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -2380,7 +2968,7 @@
         <v>21</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>391</v>
+        <v>571</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -2474,7 +3062,7 @@
         <v>21</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>389</v>
+        <v>570</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -2568,7 +3156,7 @@
         <v>21</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>388</v>
+        <v>569</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -2662,7 +3250,7 @@
         <v>21</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>387</v>
+        <v>567</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -2756,7 +3344,7 @@
         <v>21</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>374</v>
+        <v>555</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -2886,7 +3474,7 @@
         <v>21</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>384</v>
+        <v>566</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -3023,7 +3611,7 @@
         <v>21</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>360</v>
+        <v>541</v>
       </c>
       <c r="D3" t="s" s="0">
         <v>14</v>
@@ -3119,7 +3707,7 @@
         <v>21</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>406</v>
+        <v>588</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -3213,7 +3801,7 @@
         <v>21</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>380</v>
+        <v>561</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -3307,7 +3895,7 @@
         <v>21</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>394</v>
+        <v>575</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -3401,7 +3989,7 @@
         <v>21</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>383</v>
+        <v>563</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -3495,7 +4083,7 @@
         <v>21</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>396</v>
+        <v>577</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -3589,7 +4177,7 @@
         <v>21</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>405</v>
+        <v>586</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -3683,7 +4271,7 @@
         <v>21</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>379</v>
+        <v>560</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -3777,7 +4365,7 @@
         <v>21</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>393</v>
+        <v>602</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -3871,7 +4459,7 @@
         <v>21</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>372</v>
+        <v>553</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -4001,7 +4589,7 @@
         <v>21</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>381</v>
+        <v>562</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -4092,10 +4680,10 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" t="s" s="0">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>395</v>
+        <v>601</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -4189,7 +4777,7 @@
         <v>21</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>363</v>
+        <v>544</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -4288,7 +4876,7 @@
         <v>21</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>362</v>
+        <v>543</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -4387,7 +4975,7 @@
         <v>21</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>412</v>
+        <v>608</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -4486,7 +5074,7 @@
         <v>21</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>413</v>
+        <v>609</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -4585,7 +5173,7 @@
         <v>21</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>414</v>
+        <v>610</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -4684,7 +5272,7 @@
         <v>21</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>416</v>
+        <v>612</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -4780,7 +5368,7 @@
         <v>21</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>361</v>
+        <v>606</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -4876,7 +5464,7 @@
         <v>21</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>397</v>
+        <v>578</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -4972,7 +5560,7 @@
         <v>21</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>407</v>
+        <v>589</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -5066,7 +5654,7 @@
         <v>21</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>399</v>
+        <v>604</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -5162,7 +5750,7 @@
         <v>21</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>401</v>
+        <v>582</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -5258,7 +5846,7 @@
         <v>21</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>415</v>
+        <v>611</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -5357,7 +5945,7 @@
         <v>21</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>365</v>
+        <v>546</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -5449,7 +6037,7 @@
         <v>21</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>366</v>
+        <v>547</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -5541,7 +6129,7 @@
         <v>21</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>364</v>
+        <v>545</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -5633,7 +6221,7 @@
         <v>21</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>368</v>
+        <v>549</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -5722,10 +6310,10 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" t="s" s="0">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>411</v>
+        <v>607</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -5817,7 +6405,7 @@
         <v>21</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>367</v>
+        <v>548</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -5912,7 +6500,7 @@
         <v>21</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>410</v>
+        <v>592</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -6006,10 +6594,10 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" t="s" s="0">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>417</v>
+        <v>613</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -6197,7 +6785,7 @@
         <v>21</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>409</v>
+        <v>591</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -6291,7 +6879,7 @@
         <v>21</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>376</v>
+        <v>557</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">

--- a/KatalonData/IWPBootstrapData/vRelayPaymentsACH.xlsx
+++ b/KatalonData/IWPBootstrapData/vRelayPaymentsACH.xlsx
@@ -72,7 +72,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2831" uniqueCount="614">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2845" uniqueCount="621">
   <si>
     <t>Result</t>
   </si>
@@ -1914,6 +1914,27 @@
   </si>
   <si>
     <t>Fri Oct 23 02:52:20 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Oct 24 01:38:41 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Oct 24 02:13:55 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Oct 24 02:18:24 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Oct 24 02:22:54 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Oct 24 02:25:53 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Oct 24 02:27:43 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Oct 24 02:33:27 IST 2026</t>
   </si>
 </sst>
 </file>
@@ -4975,7 +4996,7 @@
         <v>21</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>608</v>
+        <v>615</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -5074,7 +5095,7 @@
         <v>21</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>609</v>
+        <v>616</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -5173,7 +5194,7 @@
         <v>21</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>610</v>
+        <v>617</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -5272,7 +5293,7 @@
         <v>21</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>612</v>
+        <v>619</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -5846,7 +5867,7 @@
         <v>21</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>611</v>
+        <v>618</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -6310,10 +6331,10 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" t="s" s="0">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>607</v>
+        <v>614</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -6594,10 +6615,10 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" t="s" s="0">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>613</v>
+        <v>620</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
